--- a/recommendations_results_2.xlsx
+++ b/recommendations_results_2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,12 +468,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Corporate Finance</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>graph</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -481,32 +481,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ECE204</t>
+          <t>CS685</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Numerical Methods</t>
+          <t>Machine Learning: Statistical and Computational Foundations</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Application of computational methods to engineering problems. Number systems, errors and error propagation. Roots of nonlinear equations. Introduction to numerical linear algebra. Interpolation and numerical integration. Introduction to numerical solutions of ordinary differential equations, optimization. Emphasis will be placed on algorithm development.</t>
+          <t>Extracting meaningful patterns from random samples of large data sets.  Statistical analysis of the resulting problems. Common algorithm paradigms for such tasks.  Central concepts: VC-dimension, Margins of classifier, Sparsity and description length.  Performance guarantees: Generalization bounds, data dependent error bounds and computational complexity of learning algorithms.  Common paradigms: Neural networks, Kernel methods and Support Vector machines, Applications to Data Mining.</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6377090979112175</v>
+        <v>0.00177586563957936</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Corporate Finance</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>graph</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -514,32 +514,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ECE650</t>
+          <t>CS786</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Methods and Tools for Software Engineering</t>
+          <t>Probabilistic Inference and Machine Learning</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Software Systems - Systems programming and operating systems, scripting, system calls, libraries, compilers and interpreters.  Mathematical logic - propositional &amp; predicate logic, and some higher-order logics, syntax, semantics, entailment, deduction, use of logic in software.  Data structures - lists, stacks, queues, heaps, trees, graphs, and algorithms to manipulate such data structures.  Graduate students who have previously taken ECE 750 with the topic title Methods and Tools for Software Engineering are not eligible to take ECE 650.</t>
+          <t>Covers the fundamental principles of probabilistic inference and computational learning systems. Topics include Bayes decision and utility theory, Monte Carlo and Markov chain Monte Carlo methods; learning with complete data; Bayesian networks, Markov random fields and factor graphs; models; learning with incomplete data; computational learning and PAC learning theory.</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.6044311570990034</v>
+        <v>0.001622656097008785</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Corporate Finance</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>graph</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -547,192 +547,192 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MSE700</t>
+          <t>CIVE399</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Topics in Operations Research and Management</t>
+          <t>Seminar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Priority may be given to Management Sciences students.</t>
+          <t>General seminar.</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.4895635581351766</v>
+        <v>0.001614194415674361</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Corporate Finance</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>faiss</t>
+          <t>graph</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ECE204</t>
+          <t>AMATH251</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Numerical Methods</t>
+          <t>Introduction to Differential Equations (Advanced Level)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Application of computational methods to engineering problems. Number systems, errors and error propagation. Roots of nonlinear equations. Introduction to numerical linear algebra. Interpolation and numerical integration. Introduction to numerical solutions of ordinary differential equations, optimization. Emphasis will be placed on algorithm development.</t>
+          <t>AMATH 251 is an advanced-level version of AMATH 250. This course offers a more theoretical treatment of differential equations and solution methods. In addition, emphasis will be placed on computational analysis of differential equations and on applications in science and engineering.</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.6377090811729431</v>
+        <v>0.00159161368551464</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Corporate Finance</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>faiss</t>
+          <t>graph</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ECE650</t>
+          <t>PHIL473</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Methods and Tools for Software Engineering</t>
+          <t>Special Topics in Feminist and Social Justice Praxis</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Software Systems - Systems programming and operating systems, scripting, system calls, libraries, compilers and interpreters.  Mathematical logic - propositional &amp; predicate logic, and some higher-order logics, syntax, semantics, entailment, deduction, use of logic in software.  Data structures - lists, stacks, queues, heaps, trees, graphs, and algorithms to manipulate such data structures.  Graduate students who have previously taken ECE 750 with the topic title Methods and Tools for Software Engineering are not eligible to take ECE 650.</t>
+          <t>Advanced study in special topics that emphasize practice, as announced by the department.</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.60443115234375</v>
+        <v>0.001556011752773465</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Corporate Finance</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>faiss</t>
+          <t>graph</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MSE700</t>
+          <t>PLAN627</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Topics in Operations Research and Management</t>
+          <t>Climate Change and Community Planning</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Priority may be given to Management Sciences students.</t>
+          <t>Climate change has complex implications for communities across Canada and Planners are at the forefront of developing and implementing strategies to both reduce greenhouse gas (GHG) emissions and build resilience to current and future climate. This course focuses on some of the opportunities and challenges associated with the integration of climate change into urban and rural planning, including climate vulnerability of urban systems, low-carbon transport systems, urban greening and green infrastructure for climate resilience, regenerative designs that reduce social vulnerability, the role of information and communication technologies for system efficiency and resilience, and assessing synergies and conflicts between mitigation and adaptation. Leading policy and design cases from communities across Canada and internationally will be examined.</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.4895635843276978</v>
+        <v>0.001549832980026356</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Corporate Finance</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>fuzzy_multi</t>
+          <t>graph</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ECE730</t>
+          <t>HLTHGERON459</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Special Topics in Solid State Devices</t>
+          <t>Social Neurobiology of Eating</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Special Topics in Solid State Devices</t>
+          <t>This course examines the social and neurobiological dimensions of eating. Using methods from behavioral sciences, neurosciences, and population health, we will explore the ways in which homeostasis, hedonic indulgence, social conformity together explain why we eat what we do. Topics will include brain representation of taste, neural and social dimensions of the flavour experience, self-control processes in eating, and neural gating and potentiation of social cognitive processes involving food.</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.3927536231884058</v>
+        <v>0.0014931790710674</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Corporate Finance</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fuzzy_multi</t>
+          <t>graph</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ECE750</t>
+          <t>HLTHGERON455</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Special Topics in Computer Software</t>
+          <t>Disease Mapping and Geographic Information Systems</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Special Topics in Computer Software</t>
+          <t>This course introduces disease mapping. It covers what, why, and how concerning disease mapping with a focus on how. Through hands-on experience with Geographic Information Systems (GIS), students learn how to produce maps for displaying and analyzing geographic patterns of diseases. They also learn how to identify locations of disease clusters and obtain clues as to the disease etiology.</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.3376254180602007</v>
+        <v>0.001447984925126858</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Corporate Finance</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -741,130 +741,130 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MSE200A</t>
+          <t>PHYS449</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Seminar</t>
+          <t>Machine Learning in Physics</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>General seminar.</t>
+          <t>Machine learning applications in the physical sciences.</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.3234848484848485</v>
+        <v>0.5777961888980945</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Corporate Finance</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>bert</t>
+          <t>fuzzy_multi</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MSE700</t>
+          <t>CS860</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Topics in Operations Research and Management</t>
+          <t>Advanced Topics in Algorithms and Complexity</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Priority may be given to Management Sciences students.</t>
+          <t>Advanced Topics in Algorithms and Complexity</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.5094438195228577</v>
+        <v>0.437708719851577</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Corporate Finance</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>bert</t>
+          <t>fuzzy_multi</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ECE467</t>
+          <t>STATACTSC992</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Power Systems Analysis, Operations, and Markets</t>
+          <t>Seminar in Actuarial Science</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>This course provides a basic understanding of the main issues relevant to the operation, analysis, and management of power grids, and gives an introduction to the functioning of electricity markets. The course covers the following main technical and economic issues relevant to system operators, utilities and analysts: power system economic operations; short-term operation of power systems; power flow; introduction to optimal power flows; overview of electricity markets; fault calculations; and basic concepts in power system stability and control.</t>
+          <t>Seminar in Actuarial Science</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.4552980661392212</v>
+        <v>0.4214285714285714</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Corporate Finance</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>bert</t>
+          <t>fuzzy_multi</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ECE768</t>
+          <t>PSCI635</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Power System Quality</t>
+          <t>Directed Readings in Public Policy and Administration</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>This course addresses all the dimensions of Power Quality (PQ) issues including mitigation strategies. The focus is mainly on qualitative concepts and comprehensive coverage. This course introduces PQ definitions, limitations, related international standards and mathematical techniques for PQ analysis of Power Systems. Different identification, localization and classification techniques for PQ problems will be investigated. The various kinds of PQ problems and their effects on load/system equipment will be looked at in detail. Mitigation strategies like passive filtering, active and hybrid power filtering, static VAT compensation, DVR, UPQC, etc. will be investigated. Areas covered include voltage sags, interruptions, transients, flickers, harmonics and modeling and simulation of utility systems. Grounding imperfection as a major cause for PQ problems will be addressed in detail. Moreover, the requirements and impacts of distributed generation (DG) on network power quality will be studies in detail. Effects of DG on voltage regulation, relaying losses, islanding and standards will be examined. Background Required - Basic understanding of modeling of power system elements and analysis techniques. Familiarity wit a programming language and/or a simulation package such as EMTDC/PSCAD and MATLAB is desirable.</t>
+          <t>Directed Readings in Public Policy and Administration</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.3683966994285583</v>
+        <v>0.4200121285627653</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Financial Analysis</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -873,31 +873,31 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MSE750</t>
+          <t>CS399</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Topics in Organizational Analysis and Behaviour</t>
+          <t>Readings in Computer Science</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Priority may be given to Management Sciences students.</t>
+          <t>Reading course as announced by the School.</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.3302564102564103</v>
+        <v>0.4058376839107736</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Financial Analysis</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -906,31 +906,31 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ECE780</t>
+          <t>EARTH491</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Special Topics in Control</t>
+          <t>Special Topics in Earth and Environmental Sciences</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Special Topics in Control</t>
+          <t>A lecture course offered in a particular area of Earth and Environmental Sciences, subject to availablity of instructor.</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.3013565891472869</v>
+        <v>0.4027284339946509</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Financial Analysis</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -939,333 +939,333 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ECE720</t>
+          <t>HIST701</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Special Topics in Computers and Digital Systems Software</t>
+          <t>Major Field Oral Qualifying Examination</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Special Topics in Computers and Digital Systems Software</t>
+          <t>Major Field Oral Qualifying Examination</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.3002252252252253</v>
+        <v>0.4021261516654855</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Financial Analysis</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>bert</t>
+          <t>fuzzy_multi</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MSE700</t>
+          <t>ECE700</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Topics in Operations Research and Management</t>
+          <t>Special Topics in Electrical and Computer Engineering</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Priority may be given to Management Sciences students.</t>
+          <t>Special Topics in Electrical and Computer Engineering</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.6910018920898438</v>
+        <v>0.4016907216494846</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Financial Analysis</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>bert</t>
+          <t>keyword_overlap</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ECE467</t>
+          <t>PHYS449</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Power Systems Analysis, Operations, and Markets</t>
+          <t>Machine Learning in Physics</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>This course provides a basic understanding of the main issues relevant to the operation, analysis, and management of power grids, and gives an introduction to the functioning of electricity markets. The course covers the following main technical and economic issues relevant to system operators, utilities and analysts: power system economic operations; short-term operation of power systems; power flow; introduction to optimal power flows; overview of electricity markets; fault calculations; and basic concepts in power system stability and control.</t>
+          <t>Machine learning applications in the physical sciences.</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.4949628114700317</v>
+        <v>2.449489742783178</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Financial Analysis</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>bert</t>
+          <t>keyword_overlap</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ECE768</t>
+          <t>STATACTSC992</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Power System Quality</t>
+          <t>Seminar in Actuarial Science</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>This course addresses all the dimensions of Power Quality (PQ) issues including mitigation strategies. The focus is mainly on qualitative concepts and comprehensive coverage. This course introduces PQ definitions, limitations, related international standards and mathematical techniques for PQ analysis of Power Systems. Different identification, localization and classification techniques for PQ problems will be investigated. The various kinds of PQ problems and their effects on load/system equipment will be looked at in detail. Mitigation strategies like passive filtering, active and hybrid power filtering, static VAT compensation, DVR, UPQC, etc. will be investigated. Areas covered include voltage sags, interruptions, transients, flickers, harmonics and modeling and simulation of utility systems. Grounding imperfection as a major cause for PQ problems will be addressed in detail. Moreover, the requirements and impacts of distributed generation (DG) on network power quality will be studies in detail. Effects of DG on voltage regulation, relaying losses, islanding and standards will be examined. Background Required - Basic understanding of modeling of power system elements and analysis techniques. Familiarity wit a programming language and/or a simulation package such as EMTDC/PSCAD and MATLAB is desirable.</t>
+          <t>Seminar in Actuarial Science</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.3716764450073242</v>
+        <v>1.732050807568877</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Business Operations</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>keyword_overlap</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ECE499</t>
+          <t>ECE250</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Engineering Project</t>
+          <t>Algorithms and Data Structures</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>An engineering project requiring the student to demonstrate initiative and assume responsibility. The student will arrange for a faculty supervisor prior to registration. Students can propose their own topic. A project report is required at the end of the term.</t>
+          <t>Data structures, abstract data types, recursive algorithms, algorithm analysis, sorting and searching, and problem-solving strategies.</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.7958954649043387</v>
+        <v>1.664100588675687</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Business Operations</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>keyword_overlap</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MSE734</t>
+          <t>GEOG484</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Network Models and Applications</t>
+          <t>Machine Learning in Geospatial Science</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>This course treats the broad subject of network models. Network flow problems form a special class of linear programming that arise in a wide variety of applications including transportation, telecommunications, logistics and supply chain management. The purpose is to study the properties of network flow models, to discuss extensions and various solutions approaches, and to survey some applications.</t>
+          <t>An in-depth study of current machine learning algorithms and their applications in geospatial science, with a focus on earth observation data processing and analysis. Topics include k-nearest neighbour, decision trees, support vector machines, ensemble learning, and some deep neural networks (e.g., CNN, U-Net). Machine learning algorithms implemented using Python will be applied for semantic segmentation, land use and land cover classification, and building and road detection using aerial and satellite images.</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.5408999360305609</v>
+        <v>1.571428571428571</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Business Operations</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>keyword_overlap</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ECE204</t>
+          <t>CS840</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Numerical Methods</t>
+          <t>Advanced Topics in Data Structures</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Application of computational methods to engineering problems. Number systems, errors and error propagation. Roots of nonlinear equations. Introduction to numerical linear algebra. Interpolation and numerical integration. Introduction to numerical solutions of ordinary differential equations, optimization. Emphasis will be placed on algorithm development.</t>
+          <t>Advanced Topics in Data Structures</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.4976803452485005</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Business Operations</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>faiss</t>
+          <t>keyword_overlap</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ECE499</t>
+          <t>CS848</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Engineering Project</t>
+          <t>Advanced Topics in Data Bases</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>An engineering project requiring the student to demonstrate initiative and assume responsibility. The student will arrange for a faculty supervisor prior to registration. Students can propose their own topic. A project report is required at the end of the term.</t>
+          <t>Advanced Topics in Data Bases</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.7958954572677612</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Business Operations</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>faiss</t>
+          <t>keyword_overlap</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MSE734</t>
+          <t>CS860</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Network Models and Applications</t>
+          <t>Advanced Topics in Algorithms and Complexity</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>This course treats the broad subject of network models. Network flow problems form a special class of linear programming that arise in a wide variety of applications including transportation, telecommunications, logistics and supply chain management. The purpose is to study the properties of network flow models, to discuss extensions and various solutions approaches, and to survey some applications.</t>
+          <t>Advanced Topics in Algorithms and Complexity</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.540899932384491</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Business Operations</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>faiss</t>
+          <t>keyword_overlap</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ECE204</t>
+          <t>STATACTSC870</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Numerical Methods</t>
+          <t>Short Course in Actuarial Science</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Application of computational methods to engineering problems. Number systems, errors and error propagation. Roots of nonlinear equations. Introduction to numerical linear algebra. Interpolation and numerical integration. Introduction to numerical solutions of ordinary differential equations, optimization. Emphasis will be placed on algorithm development.</t>
+          <t>Short Course in Actuarial Science</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.4976803958415985</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Business Operations</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>fuzzy_multi</t>
+          <t>bert</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1273,32 +1273,32 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ECE102</t>
+          <t>HLTHGERON427</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Information Session</t>
+          <t>Dementia Care</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Scheduled, non-credit session to provide information to electrical and computer engineering students.</t>
+          <t>This course provides a comprehensive examination of dementia from multiple perspectives, including the person living with dementia, family care partners, and the health and social care systems. Key topics include epidemiology, prevention, stigma, meaningful engagement, care, and support.</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.359859649122807</v>
+        <v>0.6339994668960571</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Business Operations</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>fuzzy_multi</t>
+          <t>bert</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1306,32 +1306,32 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ECE201</t>
+          <t>HLTHGERON430</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Information Session</t>
+          <t>Geriatric Medicine and Health Care</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Scheduled, non-credit session to provide information to electrical and computer engineering students.</t>
+          <t>Why do some people age well, and others don't? How do we care for them? This course will address the role of geriatric medicine in the context of an aging population and provide in-depth coverage of frailty and geriatric syndromes. Students will practice critical appraisal skills of geriatric literature, and apply these to understanding how system design, interprofessional care, and geriatric medicine can improve outcomes for older persons. Students will also have the opportunity to learn about health system issues directly from stakeholders.</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.359859649122807</v>
+        <v>0.6339994668960571</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Business Operations</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>fuzzy_multi</t>
+          <t>bert</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1339,27 +1339,27 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ECE202</t>
+          <t>HLTHGERON459</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Information Session</t>
+          <t>Social Neurobiology of Eating</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Scheduled, non-credit session to provide information to electrical and computer engineering students.</t>
+          <t>This course examines the social and neurobiological dimensions of eating. Using methods from behavioral sciences, neurosciences, and population health, we will explore the ways in which homeostasis, hedonic indulgence, social conformity together explain why we eat what we do. Topics will include brain representation of taste, neural and social dimensions of the flavour experience, self-control processes in eating, and neural gating and potentiation of social cognitive processes involving food.</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.359859649122807</v>
+        <v>0.6141103506088257</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Business Operations</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1368,31 +1368,31 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>MSE605</t>
+          <t>REN262R</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Organizational Behaviour</t>
+          <t>Manga</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Introduction to the concepts of learning, person perception, attitudes, and motivation in an organization. Consideration of communication, roles, norms, and decision making within a group. Discussion of power, control, leadership, and management in light of the above concepts. Priority may be given to Management Sciences students.</t>
+          <t>Manga is graphic narrative from Japan that draws on complex historical contexts, global influences, and stylistic conventions in order to create a unique storytelling medium. By studying manga texts such as Dororo, Akira, and Deathnote, students in this course will be encouraged to think critically about visual narrative, cultural values in a global marketplace, and literature as a concept.</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.512759804725647</v>
+        <v>0.5983653664588928</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Business Operations</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1401,31 +1401,31 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>MSE734</t>
+          <t>PHIL473</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Network Models and Applications</t>
+          <t>Special Topics in Feminist and Social Justice Praxis</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>This course treats the broad subject of network models. Network flow problems form a special class of linear programming that arise in a wide variety of applications including transportation, telecommunications, logistics and supply chain management. The purpose is to study the properties of network flow models, to discuss extensions and various solutions approaches, and to survey some applications.</t>
+          <t>Advanced study in special topics that emphasize practice, as announced by the department.</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.4768384397029877</v>
+        <v>0.5959513783454895</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Business Operations</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1434,421 +1434,91 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ECE665</t>
+          <t>PLAN627</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>High Voltage Engineering Applications</t>
+          <t>Climate Change and Community Planning</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>This course deals with the new emerging technology in high voltage engineering. It is divided into five parts. The first part of the course in a review of the basic fundamentals of high voltage engineering. The second part deals with the new techniques in partial discharge measurements. The third part of the course deals with measurements of charge distribution in solid dielectric. The fourth part of the course discusses the optical fiber based monitoring techniques of the high voltage high power equipment. The last part of the course deals with the application of high voltage engineering in power systems.</t>
+          <t>Climate change has complex implications for communities across Canada and Planners are at the forefront of developing and implementing strategies to both reduce greenhouse gas (GHG) emissions and build resilience to current and future climate. This course focuses on some of the opportunities and challenges associated with the integration of climate change into urban and rural planning, including climate vulnerability of urban systems, low-carbon transport systems, urban greening and green infrastructure for climate resilience, regenerative designs that reduce social vulnerability, the role of information and communication technologies for system efficiency and resilience, and assessing synergies and conflicts between mitigation and adaptation. Leading policy and design cases from communities across Canada and internationally will be examined.</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.4646884202957153</v>
+        <v>0.589813232421875</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>bert</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ECE6617PD</t>
+          <t>ARTSDEAN317</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Asset Management and Risk Assessment of Power Systems</t>
+          <t>Afro-Latin America</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>The course will discuss in detail the basic concepts of risk assessment and outage models of system components.  It will discuss in details the concept of asset management and its main components, application examples about the risk evaluation of transmission lines, generators and substations will be considered.</t>
+          <t>The African diaspora is central to understanding the historical development and contemporary expressions of Latin American identity. Through the study of historical events, cultural production, and current affairs, this course examines African cultural legacies in Latin America, and explains the economic, societal, and political challenges faced by Afro-Latin Americans today.</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.6678971247208291</v>
+        <v>0.5695852637290955</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>machine learning algorithms and data science</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>bert</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ECE666</t>
+          <t>VPA329</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Power Systems Operation</t>
+          <t>Sustainability Integration Consulting Group - Senior Strategist</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>The course deals in details of power system operation in the context of restructured electricity markets. Basics of power system operation - economic load dispatch, concept of marginal cost, Kuhn-Tucker's conditions of optimum, unit commitments, hydro-thermal coordination, optimal power flow analysis and security constrained economic dispatch are introduced.  On the topic of transmission open access, the course discusses transmission pricing paradigms and the role of distribution factors in pricing.  Transmission operations cover congestion management methods and firm transmission rights.  Ancillary services procurement and pricing and power system security are discussed.  Background - ECE 467 or equivalent.</t>
+          <t>This course provides students hands-on training in strategic integration of sustainability objectives and measurement within the firm with guidance from industry experts and supervision by faculty. This course is normally taken after a student has completed one term as a junior strategist with the consulting group. Senior strategists interface with firm representatives, lead the consulting student team, and oversee consulting reports/recommendations.</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0.583307291664018</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>cosine</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>3</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>ECE650</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Methods and Tools for Software Engineering</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Software Systems - Systems programming and operating systems, scripting, system calls, libraries, compilers and interpreters.  Mathematical logic - propositional &amp; predicate logic, and some higher-order logics, syntax, semantics, entailment, deduction, use of logic in software.  Data structures - lists, stacks, queues, heaps, trees, graphs, and algorithms to manipulate such data structures.  Graduate students who have previously taken ECE 750 with the topic title Methods and Tools for Software Engineering are not eligible to take ECE 650.</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>0.5019940828098385</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>faiss</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>ECE6617PD</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Asset Management and Risk Assessment of Power Systems</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>The course will discuss in detail the basic concepts of risk assessment and outage models of system components.  It will discuss in details the concept of asset management and its main components, application examples about the risk evaluation of transmission lines, generators and substations will be considered.</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>0.66789710521698</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>faiss</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>2</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>ECE666</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Power Systems Operation</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>The course deals in details of power system operation in the context of restructured electricity markets. Basics of power system operation - economic load dispatch, concept of marginal cost, Kuhn-Tucker's conditions of optimum, unit commitments, hydro-thermal coordination, optimal power flow analysis and security constrained economic dispatch are introduced.  On the topic of transmission open access, the course discusses transmission pricing paradigms and the role of distribution factors in pricing.  Transmission operations cover congestion management methods and firm transmission rights.  Ancillary services procurement and pricing and power system security are discussed.  Background - ECE 467 or equivalent.</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>0.5833073258399963</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>faiss</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>3</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>ECE650</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Methods and Tools for Software Engineering</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Software Systems - Systems programming and operating systems, scripting, system calls, libraries, compilers and interpreters.  Mathematical logic - propositional &amp; predicate logic, and some higher-order logics, syntax, semantics, entailment, deduction, use of logic in software.  Data structures - lists, stacks, queues, heaps, trees, graphs, and algorithms to manipulate such data structures.  Graduate students who have previously taken ECE 750 with the topic title Methods and Tools for Software Engineering are not eligible to take ECE 650.</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>0.5019940733909607</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>fuzzy_multi</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>ECE730</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Special Topics in Solid State Devices</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Special Topics in Solid State Devices</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>0.4177272727272727</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>fuzzy_multi</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>2</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>ECE780</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Special Topics in Control</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Special Topics in Control</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>0.3598837209302326</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>fuzzy_multi</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>3</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>MSE200A</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Seminar</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>General seminar.</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>0.3498823529411765</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>bert</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>MSE700</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Topics in Operations Research and Management</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Priority may be given to Management Sciences students.</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>0.3441675305366516</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>bert</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>2</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>ECE467</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Power Systems Analysis, Operations, and Markets</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>This course provides a basic understanding of the main issues relevant to the operation, analysis, and management of power grids, and gives an introduction to the functioning of electricity markets. The course covers the following main technical and economic issues relevant to system operators, utilities and analysts: power system economic operations; short-term operation of power systems; power flow; introduction to optimal power flows; overview of electricity markets; fault calculations; and basic concepts in power system stability and control.</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>0.2999085187911987</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>bert</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>3</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>MSE638</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Information Systems Analysis and Design</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>This course presents the foundations which underlie the development of management information systems. Emphasis is placed on the concepts, strategies, techniques and tools for identifying and specifying information systems requirements, and developing designs. Students are expected to complete an analysis and design project. Priority may be given to Management Sciences students.</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
-        <v>0.2774520516395569</v>
+        <v>0.5510664582252502</v>
       </c>
     </row>
   </sheetData>
